--- a/sample-data.xlsx
+++ b/sample-data.xlsx
@@ -443,16 +443,16 @@
         <v>ความพึงพอใจต่อภาพรวมโครงการ [สามารถนำความรู้/ทักษะไปประยุกต์ใช้ได้จริง]</v>
       </c>
       <c r="O1" t="str">
-        <v>ประเมินความสอดคล้อง 5Hs [ช่วยพัฒนาการคิดวิเคราะห์และแก้ปัญหาที่ซับซ้อน (Head/Hand)]</v>
+        <v xml:space="preserve"> [ช่วยพัฒนาการคิดวิเคราะห์และแก้ปัญหาที่ซับซ้อน (Head/Hand)]</v>
       </c>
       <c r="P1" t="str">
-        <v>ประเมินความสอดคล้อง 5Hs [ช่วยเสริมสร้างแนวคิดนวัตกรรมและความเป็นผู้ประกอบการ (Head/Hand)]</v>
+        <v xml:space="preserve"> [ช่วยเสริมสร้างแนวคิดนวัตกรรมและความเป็นผู้ประกอบการ (Head/Hand)]</v>
       </c>
       <c r="Q1" t="str">
-        <v>ประเมินความสอดคล้อง 5Hs [ช่วยพัฒนาทักษะเทคโนโลยีและการสื่อสาร (Head/Hand/Habit)]</v>
+        <v xml:space="preserve"> [ช่วยพัฒนาทักษะเทคโนโลยีและการสื่อสาร (Head/Hand/Habit)]</v>
       </c>
       <c r="R1" t="str">
-        <v>ประเมินความสอดคล้อง 5Hs [ช่วยพัฒนาความฉลาดทางอารมณ์และพฤติกรรมแบบมืออาชีพ (Head/Heart/Habit)]</v>
+        <v xml:space="preserve"> [ช่วยพัฒนาความฉลาดทางอารมณ์และพฤติกรรมแบบมืออาชีพ (Head/Heart/Habit)]</v>
       </c>
       <c r="S1" t="str">
         <v>SDG 1 : No Poverty ขจัดความยากจน โครงการมีส่วนช่วยลดภาระค่าใช้จ่าย หรือเพิ่มโอกาสในการเข้าถึงทรัพยากรและการพัฒนาคุณภาพชีวิตของผู้เข้าร่วมหรือชุมชน</v>
@@ -625,7 +625,7 @@
         <v>5</v>
       </c>
       <c r="AI2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ2">
         <v>3</v>
@@ -2752,7 +2752,7 @@
         <v>4</v>
       </c>
       <c r="L20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M20">
         <v>4</v>
@@ -4633,7 +4633,7 @@
         <v>4</v>
       </c>
       <c r="AC35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD35">
         <v>5</v>
@@ -6772,7 +6772,7 @@
         <v>4</v>
       </c>
       <c r="J53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K53">
         <v>3</v>
@@ -7195,7 +7195,7 @@
         <v>4</v>
       </c>
       <c r="AC56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD56">
         <v>5</v>
@@ -8733,10 +8733,10 @@
         <v>4</v>
       </c>
       <c r="M69">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O69">
         <v>5</v>
@@ -9343,7 +9343,7 @@
         <v>2</v>
       </c>
       <c r="M74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N74">
         <v>4</v>
@@ -9834,7 +9834,7 @@
         <v>4</v>
       </c>
       <c r="N78">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78">
         <v>2</v>
@@ -10248,7 +10248,7 @@
         <v>3</v>
       </c>
       <c r="AD81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE81">
         <v>3</v>
@@ -11120,7 +11120,7 @@
         <v>5</v>
       </c>
       <c r="AJ88">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK88">
         <v>5</v>
@@ -11248,7 +11248,7 @@
         <v>5</v>
       </c>
       <c r="AL89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM89">
         <v>4</v>
